--- a/Iwaniuk_etal_1999/Iwaniuk_etal_1999_Table1_snapshot.xlsx
+++ b/Iwaniuk_etal_1999/Iwaniuk_etal_1999_Table1_snapshot.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://computingservices-my.sharepoint.com/personal/mg2544_bath_ac_uk/Documents/Research Schemes/Allen Institue/Evo-M1-Trait-Data/Iwaniuk_etal_1999/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_F25DC773A252ABDACC1048E3599F62A65ADE58E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBE1F451-774B-4B66-8C05-3146AA55188C}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_F25DC773A252ABDACC1048E3599F62A65ADE58E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8574F9FB-F6F4-4768-9D47-702E05443666}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -478,17 +478,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -498,30 +492,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -531,14 +510,29 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -556,6 +550,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -821,826 +819,694 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.36328125" customWidth="1"/>
-    <col min="4" max="4" width="17.26953125" customWidth="1"/>
-    <col min="6" max="6" width="5.26953125" customWidth="1"/>
-    <col min="7" max="7" width="14.26953125" customWidth="1"/>
-    <col min="8" max="8" width="12.7265625" customWidth="1"/>
-    <col min="9" max="9" width="13.26953125" customWidth="1"/>
-    <col min="10" max="10" width="12.26953125" customWidth="1"/>
-    <col min="11" max="11" width="15.54296875" customWidth="1"/>
+    <col min="2" max="2" width="23.453125" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" customWidth="1"/>
+    <col min="4" max="4" width="14.26953125" customWidth="1"/>
+    <col min="5" max="5" width="12.7265625" customWidth="1"/>
+    <col min="6" max="6" width="13.26953125" customWidth="1"/>
+    <col min="7" max="7" width="12.26953125" customWidth="1"/>
+    <col min="8" max="8" width="15.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="19"/>
-      <c r="G1" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="17" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="F1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="G1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="H1" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3" t="s">
+      <c r="C2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="5">
+      <c r="E2" s="3">
         <v>4</v>
       </c>
-      <c r="I2" s="5">
+      <c r="F2" s="3">
         <v>4</v>
       </c>
-      <c r="J2" s="5">
+      <c r="G2" s="3">
         <v>0</v>
       </c>
-      <c r="K2" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
+      <c r="H2" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="8" t="s">
+      <c r="C3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="9" t="s">
+      <c r="D3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="10">
-        <v>2</v>
-      </c>
-      <c r="I3" s="10">
+      <c r="E3" s="6">
+        <v>2</v>
+      </c>
+      <c r="F3" s="6">
         <v>0</v>
       </c>
-      <c r="J3" s="10">
-        <v>2</v>
-      </c>
-      <c r="K3" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
+      <c r="G3" s="6">
+        <v>2</v>
+      </c>
+      <c r="H3" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="8" t="s">
+      <c r="C4" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="9" t="s">
+      <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="10">
-        <v>1</v>
-      </c>
-      <c r="I4" s="10">
+      <c r="E4" s="6">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6">
         <v>0</v>
       </c>
-      <c r="J4" s="10">
+      <c r="G4" s="6">
         <v>0</v>
       </c>
-      <c r="K4" s="10">
+      <c r="H4" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="8" t="s">
+      <c r="C5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="9" t="s">
+      <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="10">
+      <c r="E5" s="6">
         <v>5</v>
       </c>
-      <c r="I5" s="10">
+      <c r="F5" s="6">
         <v>3</v>
       </c>
-      <c r="J5" s="10">
-        <v>2</v>
-      </c>
-      <c r="K5" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
+      <c r="G5" s="6">
+        <v>2</v>
+      </c>
+      <c r="H5" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="8" t="s">
+      <c r="C6" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="9" t="s">
+      <c r="D6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="10">
+      <c r="E6" s="6">
         <v>6</v>
       </c>
-      <c r="I6" s="10">
+      <c r="F6" s="6">
         <v>3</v>
       </c>
-      <c r="J6" s="10">
-        <v>1</v>
-      </c>
-      <c r="K6" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
+      <c r="G6" s="6">
+        <v>1</v>
+      </c>
+      <c r="H6" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="8" t="s">
+      <c r="C7" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="9" t="s">
+      <c r="D7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="10">
-        <v>1</v>
-      </c>
-      <c r="I7" s="10">
+      <c r="E7" s="6">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6">
         <v>0</v>
       </c>
-      <c r="J7" s="10">
+      <c r="G7" s="6">
         <v>3</v>
       </c>
-      <c r="K7" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
+      <c r="H7" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="8" t="s">
+      <c r="C8" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="9" t="s">
+      <c r="D8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="10">
+      <c r="E8" s="6">
         <v>3</v>
       </c>
-      <c r="I8" s="10">
-        <v>2</v>
-      </c>
-      <c r="J8" s="10">
-        <v>2</v>
-      </c>
-      <c r="K8" s="10">
+      <c r="F8" s="6">
+        <v>2</v>
+      </c>
+      <c r="G8" s="6">
+        <v>2</v>
+      </c>
+      <c r="H8" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="8" t="s">
+      <c r="C9" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="9" t="s">
+      <c r="D9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="10">
-        <v>2</v>
-      </c>
-      <c r="I9" s="10">
-        <v>1</v>
-      </c>
-      <c r="J9" s="10">
+      <c r="E9" s="6">
+        <v>2</v>
+      </c>
+      <c r="F9" s="6">
+        <v>1</v>
+      </c>
+      <c r="G9" s="6">
         <v>4</v>
       </c>
-      <c r="K9" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10" s="6" t="s">
+      <c r="H9" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="8" t="s">
+      <c r="C10" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="9" t="s">
+      <c r="D10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="10">
+      <c r="E10" s="6">
         <v>5</v>
       </c>
-      <c r="I10" s="10">
+      <c r="F10" s="6">
         <v>4</v>
       </c>
-      <c r="J10" s="10">
-        <v>2</v>
-      </c>
-      <c r="K10" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="6" t="s">
+      <c r="G10" s="6">
+        <v>2</v>
+      </c>
+      <c r="H10" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="8" t="s">
+      <c r="C11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="9" t="s">
+      <c r="D11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="10">
+      <c r="E11" s="6">
         <v>7</v>
       </c>
-      <c r="I11" s="10">
-        <v>1</v>
-      </c>
-      <c r="J11" s="10">
-        <v>2</v>
-      </c>
-      <c r="K11" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="6" t="s">
+      <c r="F11" s="6">
+        <v>1</v>
+      </c>
+      <c r="G11" s="6">
+        <v>2</v>
+      </c>
+      <c r="H11" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8" t="s">
+      <c r="C12" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="9" t="s">
+      <c r="D12" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="10">
+      <c r="E12" s="6">
         <v>6</v>
       </c>
-      <c r="I12" s="10">
+      <c r="F12" s="6">
         <v>4</v>
       </c>
-      <c r="J12" s="10">
+      <c r="G12" s="6">
         <v>0</v>
       </c>
-      <c r="K12" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="6" t="s">
+      <c r="H12" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="8" t="s">
+      <c r="C13" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="9" t="s">
+      <c r="D13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H13" s="10">
+      <c r="E13" s="6">
         <v>5</v>
       </c>
-      <c r="I13" s="10">
+      <c r="F13" s="6">
         <v>4</v>
       </c>
-      <c r="J13" s="10">
-        <v>1</v>
-      </c>
-      <c r="K13" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="6" t="s">
+      <c r="G13" s="6">
+        <v>1</v>
+      </c>
+      <c r="H13" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="8" t="s">
+      <c r="C14" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="9" t="s">
+      <c r="D14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="10">
+      <c r="E14" s="6">
         <v>6</v>
       </c>
-      <c r="I14" s="10">
+      <c r="F14" s="6">
         <v>3</v>
       </c>
-      <c r="J14" s="10">
-        <v>2</v>
-      </c>
-      <c r="K14" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="6" t="s">
+      <c r="G14" s="6">
+        <v>2</v>
+      </c>
+      <c r="H14" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="8" t="s">
+      <c r="C15" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="9" t="s">
+      <c r="D15" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="10">
+      <c r="E15" s="6">
         <v>3</v>
       </c>
-      <c r="I15" s="10">
+      <c r="F15" s="6">
         <v>0</v>
       </c>
-      <c r="J15" s="10">
+      <c r="G15" s="6">
         <v>0</v>
       </c>
-      <c r="K15" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="6" t="s">
+      <c r="H15" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="8" t="s">
+      <c r="C16" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="9" t="s">
+      <c r="D16" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H16" s="10">
+      <c r="E16" s="6">
         <v>5</v>
       </c>
-      <c r="I16" s="10">
+      <c r="F16" s="6">
         <v>4</v>
       </c>
-      <c r="J16" s="10">
+      <c r="G16" s="6">
         <v>3</v>
       </c>
-      <c r="K16" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A17" s="6" t="s">
+      <c r="H16" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="8" t="s">
+      <c r="C17" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="9" t="s">
+      <c r="D17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H17" s="10">
+      <c r="E17" s="6">
         <v>6</v>
       </c>
-      <c r="I17" s="10">
-        <v>2</v>
-      </c>
-      <c r="J17" s="10">
-        <v>2</v>
-      </c>
-      <c r="K17" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A18" s="6" t="s">
+      <c r="F17" s="6">
+        <v>2</v>
+      </c>
+      <c r="G17" s="6">
+        <v>2</v>
+      </c>
+      <c r="H17" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="8" t="s">
+      <c r="C18" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="9" t="s">
+      <c r="D18" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H18" s="10">
-        <v>2</v>
-      </c>
-      <c r="I18" s="10">
+      <c r="E18" s="6">
+        <v>2</v>
+      </c>
+      <c r="F18" s="6">
         <v>0</v>
       </c>
-      <c r="J18" s="10">
+      <c r="G18" s="6">
         <v>0</v>
       </c>
-      <c r="K18" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A19" s="6" t="s">
+      <c r="H18" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="8" t="s">
+      <c r="C19" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="9" t="s">
+      <c r="D19" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H19" s="10">
+      <c r="E19" s="6">
         <v>3</v>
       </c>
-      <c r="I19" s="10">
+      <c r="F19" s="6">
         <v>3</v>
       </c>
-      <c r="J19" s="10">
-        <v>1</v>
-      </c>
-      <c r="K19" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A20" s="6" t="s">
+      <c r="G19" s="6">
+        <v>1</v>
+      </c>
+      <c r="H19" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="8" t="s">
+      <c r="C20" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F20" s="8"/>
-      <c r="G20" s="9" t="s">
+      <c r="D20" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H20" s="10">
+      <c r="E20" s="6">
         <v>3</v>
       </c>
-      <c r="I20" s="10">
-        <v>2</v>
-      </c>
-      <c r="J20" s="10">
-        <v>2</v>
-      </c>
-      <c r="K20" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A21" s="6" t="s">
+      <c r="F20" s="6">
+        <v>2</v>
+      </c>
+      <c r="G20" s="6">
+        <v>2</v>
+      </c>
+      <c r="H20" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="8" t="s">
+      <c r="C21" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="F21" s="8"/>
-      <c r="G21" s="9" t="s">
+      <c r="D21" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H21" s="10">
+      <c r="E21" s="6">
         <v>3</v>
       </c>
-      <c r="I21" s="10">
-        <v>1</v>
-      </c>
-      <c r="J21" s="10">
-        <v>1</v>
-      </c>
-      <c r="K21" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A22" s="6" t="s">
+      <c r="F21" s="6">
+        <v>1</v>
+      </c>
+      <c r="G21" s="6">
+        <v>1</v>
+      </c>
+      <c r="H21" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="8" t="s">
+      <c r="C22" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="9" t="s">
+      <c r="D22" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H22" s="10">
+      <c r="E22" s="6">
         <v>4</v>
       </c>
-      <c r="I22" s="10">
+      <c r="F22" s="6">
         <v>4</v>
       </c>
-      <c r="J22" s="10">
-        <v>2</v>
-      </c>
-      <c r="K22" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A23" s="6" t="s">
+      <c r="G22" s="6">
+        <v>2</v>
+      </c>
+      <c r="H22" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="8" t="s">
+      <c r="C23" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="8"/>
-      <c r="G23" s="9" t="s">
+      <c r="D23" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H23" s="10">
+      <c r="E23" s="6">
         <v>5</v>
       </c>
-      <c r="I23" s="10">
+      <c r="F23" s="6">
         <v>4</v>
       </c>
-      <c r="J23" s="10">
-        <v>1</v>
-      </c>
-      <c r="K23" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A24" s="6" t="s">
+      <c r="G23" s="6">
+        <v>1</v>
+      </c>
+      <c r="H23" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="8" t="s">
+      <c r="C24" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="F24" s="8"/>
-      <c r="G24" s="9" t="s">
+      <c r="D24" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="H24" s="10">
+      <c r="E24" s="6">
         <v>3</v>
       </c>
-      <c r="I24" s="10">
+      <c r="F24" s="6">
         <v>0</v>
       </c>
-      <c r="J24" s="10">
+      <c r="G24" s="6">
         <v>0</v>
       </c>
-      <c r="K24" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A25" s="6" t="s">
+      <c r="H24" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c r="B25" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="8" t="s">
+      <c r="C25" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="F25" s="8"/>
-      <c r="G25" s="9" t="s">
+      <c r="D25" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H25" s="10">
+      <c r="E25" s="6">
         <v>3</v>
       </c>
-      <c r="I25" s="10">
-        <v>2</v>
-      </c>
-      <c r="J25" s="10">
-        <v>1</v>
-      </c>
-      <c r="K25" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A26" s="12" t="s">
+      <c r="F25" s="6">
+        <v>2</v>
+      </c>
+      <c r="G25" s="6">
+        <v>1</v>
+      </c>
+      <c r="H25" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="7" t="s">
         <v>69</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="14" t="s">
+      <c r="C26" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F26" s="14"/>
-      <c r="G26" s="15" t="s">
+      <c r="D26" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="H26" s="16">
+      <c r="E26" s="9">
         <v>3</v>
       </c>
-      <c r="I26" s="16">
-        <v>2</v>
-      </c>
-      <c r="J26" s="16">
+      <c r="F26" s="9">
+        <v>2</v>
+      </c>
+      <c r="G26" s="9">
         <v>3</v>
       </c>
-      <c r="K26" s="16">
+      <c r="H26" s="9">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="52">
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Iwaniuk_etal_1999/Iwaniuk_etal_1999_Table1_snapshot.xlsx
+++ b/Iwaniuk_etal_1999/Iwaniuk_etal_1999_Table1_snapshot.xlsx
@@ -1509,4 +1509,276 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66631731-AD51-49D4-8BE1-A550631DA10E}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F68FBD3-80A1-4D07-A3CD-05457DD3F3EF}"/>
 </file>